--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20211.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20211.xlsx
@@ -471,19 +471,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>80.95</v>
+        <v>90.48</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -497,19 +497,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>65.79000000000001</v>
+        <v>81.58</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -562,16 +562,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>90.48</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +588,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>81.58</v>
+      </c>
+      <c r="H3">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -647,19 +653,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>80.95</v>
+        <v>90.48</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -673,19 +679,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>65.79000000000001</v>
+        <v>81.58</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20211.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20211.xlsx
@@ -562,19 +562,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>90.48</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -588,19 +588,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>81.58</v>
+        <v>89.47</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -656,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>90.48</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>81.58</v>
+        <v>89.47</v>
       </c>
       <c r="H3">
         <v>7.8</v>
